--- a/Coherent model.xlsx
+++ b/Coherent model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Davide/Library/Mobile Documents/com~apple~CloudDocs/Claude/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF6C581-E8AF-B24E-9578-82B5491360DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{977971E4-8FF0-C642-8A08-137855E594F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Operating model" sheetId="1" r:id="rId1"/>
@@ -251,7 +251,7 @@
         <t>[Commento in thread]
 La versione di Excel in uso consente di leggere questo commento in thread, ma tutte le modifiche a esso apportate verranno rimosse se il file viene aperto in una versione più recente di Excel. Ulteriori informazioni: https://go.microsoft.com/fwlink/?linkid=870924
 Commento:
-Finestra di rischio ciclico, decelerazione. Fine della fase supply-constrained</t>
+Finestra di rischio ciclico, decelerazione</t>
       </text>
     </comment>
     <comment ref="C8" authorId="2" shapeId="0" xr:uid="{8E0A18C6-AB34-494D-9E10-F11FF18F3106}">
@@ -430,7 +430,7 @@
         <t>[Commento in thread]
 La versione di Excel in uso consente di leggere questo commento in thread, ma tutte le modifiche a esso apportate verranno rimosse se il file viene aperto in una versione più recente di Excel. Ulteriori informazioni: https://go.microsoft.com/fwlink/?linkid=870924
 Commento:
-From 10K, Note "goodwill and other intangible assets"</t>
+Da 10K, Note "goodwill and other intangible assets"</t>
       </text>
     </comment>
     <comment ref="G59" authorId="23" shapeId="0" xr:uid="{481BF65E-C450-2046-9CB6-4C52712BCBA8}">
@@ -438,7 +438,7 @@
         <t>[Commento in thread]
 La versione di Excel in uso consente di leggere questo commento in thread, ma tutte le modifiche a esso apportate verranno rimosse se il file viene aperto in una versione più recente di Excel. Ulteriori informazioni: https://go.microsoft.com/fwlink/?linkid=870924
 Commento:
-From 10K, Note "goodwill and other intangible assets"</t>
+Da 10K, Note "goodwill and other intangible assets"</t>
       </text>
     </comment>
     <comment ref="H59" authorId="24" shapeId="0" xr:uid="{1FE5549F-06AB-1E40-9A7D-5F58ED7FE863}">
@@ -446,7 +446,7 @@
         <t>[Commento in thread]
 La versione di Excel in uso consente di leggere questo commento in thread, ma tutte le modifiche a esso apportate verranno rimosse se il file viene aperto in una versione più recente di Excel. Ulteriori informazioni: https://go.microsoft.com/fwlink/?linkid=870924
 Commento:
-From 10K, Note "goodwill and other intangible assets"</t>
+Da 10K, Note "goodwill and other intangible assets"</t>
       </text>
     </comment>
     <comment ref="I59" authorId="25" shapeId="0" xr:uid="{752831E2-0212-A04A-8F48-852F04160AA9}">
@@ -454,7 +454,7 @@
         <t>[Commento in thread]
 La versione di Excel in uso consente di leggere questo commento in thread, ma tutte le modifiche a esso apportate verranno rimosse se il file viene aperto in una versione più recente di Excel. Ulteriori informazioni: https://go.microsoft.com/fwlink/?linkid=870924
 Commento:
-From 10K, Note "goodwill and other intangible assets"</t>
+Da 10K, Note "goodwill and other intangible assets"</t>
       </text>
     </comment>
     <comment ref="J59" authorId="26" shapeId="0" xr:uid="{4F645672-C2D9-DD4F-B60A-6987DC8088CB}">
@@ -462,7 +462,7 @@
         <t>[Commento in thread]
 La versione di Excel in uso consente di leggere questo commento in thread, ma tutte le modifiche a esso apportate verranno rimosse se il file viene aperto in una versione più recente di Excel. Ulteriori informazioni: https://go.microsoft.com/fwlink/?linkid=870924
 Commento:
-From 10K, Note "goodwill and other intangible assets"</t>
+Da 10K, Note "goodwill and other intangible assets"</t>
       </text>
     </comment>
     <comment ref="K59" authorId="27" shapeId="0" xr:uid="{2927FECF-3E87-F847-9A68-D2D69E7D02AE}">
@@ -470,7 +470,7 @@
         <t>[Commento in thread]
 La versione di Excel in uso consente di leggere questo commento in thread, ma tutte le modifiche a esso apportate verranno rimosse se il file viene aperto in una versione più recente di Excel. Ulteriori informazioni: https://go.microsoft.com/fwlink/?linkid=870924
 Commento:
-Residuo oltre l'orizzonte della nota diviso per 4 anni</t>
+Residuo oltre l'orizzonte della nota diviso per 5 anni</t>
       </text>
     </comment>
     <comment ref="J60" authorId="28" shapeId="0" xr:uid="{F3D82ADF-A868-7047-A97B-51E021E12F4E}">
@@ -697,7 +697,7 @@
         <t>[Commento in thread]
 La versione di Excel in uso consente di leggere questo commento in thread, ma tutte le modifiche a esso apportate verranno rimosse se il file viene aperto in una versione più recente di Excel. Ulteriori informazioni: https://go.microsoft.com/fwlink/?linkid=870924
 Commento:
-From 10K</t>
+Da 10K</t>
       </text>
     </comment>
   </commentList>
@@ -2687,7 +2687,7 @@
     <text>Fade trimestrale</text>
   </threadedComment>
   <threadedComment ref="K7" dT="2026-08-22T08:16:36.45" personId="{F89EDB22-7672-F645-92D6-BD25E4A6FC47}" id="{9FF27733-8D21-D343-B6E3-D9AE3A8247B5}">
-    <text>Finestra di rischio ciclico, decelerazione. Fine della fase supply-constrained</text>
+    <text>Finestra di rischio ciclico, decelerazione</text>
   </threadedComment>
   <threadedComment ref="C8" dT="2026-09-02T07:54:35.56" personId="{F89EDB22-7672-F645-92D6-BD25E4A6FC47}" id="{8E0A18C6-AB34-494D-9E10-F11FF18F3106}">
     <text>Fade trimestrale</text>
@@ -2761,22 +2761,22 @@
 --&gt; Media ricavi incrementali= 2,1</text>
   </threadedComment>
   <threadedComment ref="F59" dT="2026-08-24T07:34:14.86" personId="{F89EDB22-7672-F645-92D6-BD25E4A6FC47}" id="{61F1627B-87E2-6042-84F8-A58211011B44}">
-    <text>From 10K, Note "goodwill and other intangible assets"</text>
+    <text>Da 10K, Note "goodwill and other intangible assets"</text>
   </threadedComment>
   <threadedComment ref="G59" dT="2026-08-24T07:34:27.86" personId="{F89EDB22-7672-F645-92D6-BD25E4A6FC47}" id="{481BF65E-C450-2046-9CB6-4C52712BCBA8}">
-    <text>From 10K, Note "goodwill and other intangible assets"</text>
+    <text>Da 10K, Note "goodwill and other intangible assets"</text>
   </threadedComment>
   <threadedComment ref="H59" dT="2026-08-24T07:34:33.68" personId="{F89EDB22-7672-F645-92D6-BD25E4A6FC47}" id="{1FE5549F-06AB-1E40-9A7D-5F58ED7FE863}">
-    <text>From 10K, Note "goodwill and other intangible assets"</text>
+    <text>Da 10K, Note "goodwill and other intangible assets"</text>
   </threadedComment>
   <threadedComment ref="I59" dT="2026-08-24T07:34:39.08" personId="{F89EDB22-7672-F645-92D6-BD25E4A6FC47}" id="{752831E2-0212-A04A-8F48-852F04160AA9}">
-    <text>From 10K, Note "goodwill and other intangible assets"</text>
+    <text>Da 10K, Note "goodwill and other intangible assets"</text>
   </threadedComment>
   <threadedComment ref="J59" dT="2026-08-24T07:34:50.32" personId="{F89EDB22-7672-F645-92D6-BD25E4A6FC47}" id="{4F645672-C2D9-DD4F-B60A-6987DC8088CB}">
-    <text>From 10K, Note "goodwill and other intangible assets"</text>
+    <text>Da 10K, Note "goodwill and other intangible assets"</text>
   </threadedComment>
   <threadedComment ref="K59" dT="2026-09-02T07:45:48.65" personId="{F89EDB22-7672-F645-92D6-BD25E4A6FC47}" id="{2927FECF-3E87-F847-9A68-D2D69E7D02AE}">
-    <text>Residuo oltre l'orizzonte della nota diviso per 4 anni</text>
+    <text>Residuo oltre l'orizzonte della nota diviso per 5 anni</text>
   </threadedComment>
   <threadedComment ref="J60" dT="2026-08-24T07:42:28.31" personId="{F89EDB22-7672-F645-92D6-BD25E4A6FC47}" id="{F3D82ADF-A868-7047-A97B-51E021E12F4E}">
     <text>Intangibili netti totali  = 2884,474
@@ -2882,7 +2882,7 @@
 <file path=xl/threadedComments/threadedComment5.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="C43" dT="2026-08-27T07:37:12.94" personId="{F89EDB22-7672-F645-92D6-BD25E4A6FC47}" id="{1E208810-D3BE-0E47-B72C-11BDE645AE0A}">
-    <text>From 10K</text>
+    <text>Da 10K</text>
   </threadedComment>
 </ThreadedComments>
 </file>
